--- a/file/Okta_Inventory_Demo_Test.xlsx
+++ b/file/Okta_Inventory_Demo_Test.xlsx
@@ -70,13 +70,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="002E7D32"/>
+      <color rgb="0000695C"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00C62828"/>
+      <color rgb="00B71C1C"/>
       <sz val="10"/>
     </font>
     <font>
@@ -88,12 +88,12 @@
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="00C62828"/>
+      <color rgb="00B71C1C"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="001976D2"/>
+      <color rgb="0037474F"/>
       <sz val="10"/>
     </font>
     <font>
@@ -109,7 +109,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -118,17 +118,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001A237E"/>
+        <fgColor rgb="00263238"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001976D2"/>
+        <fgColor rgb="0037474F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BBDEFB"/>
+        <fgColor rgb="00ECEFF1"/>
       </patternFill>
     </fill>
     <fill>
@@ -138,32 +138,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E7D32"/>
+        <fgColor rgb="0000695C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00E0F2F1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="006A1B9A"/>
+        <fgColor rgb="00283593"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E1BEE7"/>
+        <fgColor rgb="00E8EAF6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E65100"/>
+        <fgColor rgb="00BF360C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE0B2"/>
+        <fgColor rgb="00FBE9E7"/>
       </patternFill>
     </fill>
     <fill>
@@ -173,32 +173,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
+        <fgColor rgb="00FFF8E1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFCDD2"/>
+        <fgColor rgb="00FFEBEE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0E0E0"/>
+        <fgColor rgb="00CFD8DC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A148C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C62828"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0037474F"/>
+        <fgColor rgb="00B71C1C"/>
       </patternFill>
     </fill>
   </fills>
@@ -226,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -315,25 +305,16 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -736,7 +717,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: October 05, 2026 13:23    |    Org: Ross Stores Inc.    |    Domain: ross.okta.com</t>
+          <t>Generated: October 05, 2026 19:09    |    Org: Ross Stores Inc.    |    Domain: ross.okta.com</t>
         </is>
       </c>
     </row>
@@ -1128,20 +1109,20 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2020-01-26</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G3" s="14" t="n">
-        <v>52</v>
+        <v>200</v>
       </c>
       <c r="H3" s="14" t="inlineStr">
         <is>
-          <t>Ross-Employees</t>
+          <t>Ross-Vendors, Ross-IT-Admins, Ross-Employees</t>
         </is>
       </c>
       <c r="I3" s="14" t="inlineStr">
@@ -1178,20 +1159,20 @@
       </c>
       <c r="E4" s="17" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
+          <t>2020-02-11</t>
         </is>
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="G4" s="17" t="n">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t>Ross-Finance, Ross-HR, Ross-Contractors</t>
+          <t>Ross-HR</t>
         </is>
       </c>
       <c r="I4" s="17" t="inlineStr">
@@ -1228,20 +1209,20 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>2020-11-27</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G5" s="14" t="n">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>Ross-Finance</t>
+          <t>Ross-Finance, Ross-HR, Ross-IT-Admins</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr">
@@ -1278,20 +1259,20 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2020-10-19</t>
         </is>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>Ross-Finance, Ross-Vendors, Ross-HR</t>
+          <t>Ross-Vendors, Ross-HR</t>
         </is>
       </c>
       <c r="I6" s="17" t="inlineStr">
@@ -1328,20 +1309,20 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>2022-05-15</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="G7" s="14" t="n">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>Ross-Contractors, Ross-HR</t>
+          <t>Ross-IT-Admins, Ross-Contractors</t>
         </is>
       </c>
       <c r="I7" s="14" t="inlineStr">
@@ -1378,20 +1359,20 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>2021-01-19</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>Ross-Vendors, Ross-IT-Admins</t>
+          <t>Ross-Vendors, Ross-HR</t>
         </is>
       </c>
       <c r="I8" s="17" t="inlineStr">
@@ -1428,20 +1409,20 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>2021-08-07</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G9" s="14" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>Ross-Finance, Ross-Contractors, Ross-Vendors</t>
+          <t>Ross-HR</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
@@ -1478,20 +1459,20 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2021-09-21</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>32</v>
+        <v>153</v>
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>Ross-HR</t>
+          <t>Ross-Finance</t>
         </is>
       </c>
       <c r="I10" s="17" t="inlineStr">
@@ -1528,20 +1509,20 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2020-08-05</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G11" s="14" t="n">
-        <v>98</v>
+        <v>177</v>
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>Ross-Employees</t>
+          <t>Ross-HR, Ross-IT-Admins</t>
         </is>
       </c>
       <c r="I11" s="14" t="inlineStr">
@@ -1578,20 +1559,20 @@
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t>2020-03-28</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>172</v>
+        <v>57</v>
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>Ross-IT-Admins, Ross-Finance</t>
+          <t>Ross-HR</t>
         </is>
       </c>
       <c r="I12" s="17" t="inlineStr">
@@ -1628,20 +1609,20 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>2023-05-27</t>
+          <t>2022-02-18</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G13" s="14" t="n">
-        <v>108</v>
+        <v>198</v>
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>Ross-IT-Admins</t>
+          <t>Ross-Vendors</t>
         </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
@@ -1678,20 +1659,20 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>2020-12-05</t>
+          <t>2022-12-25</t>
         </is>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>126</v>
+        <v>24</v>
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>Ross-Finance</t>
+          <t>Ross-Contractors, Ross-IT-Admins, Ross-Vendors</t>
         </is>
       </c>
       <c r="I14" s="17" t="inlineStr">
@@ -1728,20 +1709,20 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>2022-02-23</t>
+          <t>2021-09-22</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G15" s="14" t="n">
-        <v>67</v>
+        <v>193</v>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>Ross-Finance, Ross-Employees, Ross-IT-Admins</t>
+          <t>Ross-HR, Ross-Vendors</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
@@ -1778,20 +1759,20 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t>2022-01-09</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>93</v>
+        <v>184</v>
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>Ross-Finance, Ross-IT-Admins, Ross-Employees</t>
+          <t>Ross-Employees, Ross-Finance, Ross-IT-Admins</t>
         </is>
       </c>
       <c r="I16" s="17" t="inlineStr">
@@ -1828,20 +1809,20 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>2020-08-18</t>
+          <t>2022-07-14</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G17" s="14" t="n">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>Ross-Contractors</t>
+          <t>Ross-Vendors</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
@@ -1878,20 +1859,20 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2022-02-03</t>
         </is>
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>Ross-Vendors, Ross-IT-Admins</t>
+          <t>Ross-HR, Ross-Finance, Ross-IT-Admins</t>
         </is>
       </c>
       <c r="I18" s="17" t="inlineStr">
@@ -1928,20 +1909,20 @@
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2021-03-26</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G19" s="14" t="n">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>Ross-HR</t>
+          <t>Ross-Contractors, Ross-HR</t>
         </is>
       </c>
       <c r="I19" s="14" t="inlineStr">
@@ -1978,20 +1959,20 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t>2022-01-19</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>Ross-Contractors</t>
+          <t>Ross-Employees</t>
         </is>
       </c>
       <c r="I20" s="17" t="inlineStr">
@@ -2028,20 +2009,20 @@
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>2020-05-07</t>
+          <t>2021-11-15</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="G21" s="14" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>Ross-HR, Ross-Employees</t>
+          <t>Ross-Finance, Ross-IT-Admins, Ross-Contractors</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
@@ -2078,20 +2059,20 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>Ross-IT-Admins, Ross-Finance, Ross-Employees</t>
+          <t>Ross-Vendors, Ross-Employees, Ross-IT-Admins</t>
         </is>
       </c>
       <c r="I22" s="17" t="inlineStr">
@@ -2128,20 +2109,20 @@
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>2021-01-15</t>
+          <t>2020-12-10</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G23" s="14" t="n">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>Ross-HR, Ross-Vendors</t>
+          <t>Ross-Vendors, Ross-Employees, Ross-Contractors</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr">
@@ -2178,20 +2159,20 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>2023-03-18</t>
+          <t>2021-04-03</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="G24" s="17" t="n">
-        <v>66</v>
+        <v>195</v>
       </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>Ross-Contractors</t>
+          <t>Ross-Employees</t>
         </is>
       </c>
       <c r="I24" s="17" t="inlineStr">
@@ -2228,20 +2209,20 @@
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>2024-08-10</t>
+          <t>2020-07-15</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="G25" s="14" t="n">
-        <v>129</v>
+        <v>83</v>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>Ross-Contractors, Ross-HR</t>
+          <t>Ross-Employees, Ross-Contractors, Ross-HR</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
@@ -2278,20 +2259,20 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t>2021-02-22</t>
+          <t>2021-01-12</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G26" s="17" t="n">
-        <v>34</v>
+        <v>191</v>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>Ross-Finance, Ross-Contractors, Ross-Vendors</t>
+          <t>Ross-Finance, Ross-IT-Admins</t>
         </is>
       </c>
       <c r="I26" s="17" t="inlineStr">
@@ -2328,20 +2309,20 @@
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2022-02-11</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G27" s="14" t="n">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>Ross-Employees, Ross-HR, Ross-Contractors</t>
+          <t>Ross-Finance, Ross-HR, Ross-Vendors</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
@@ -2378,20 +2359,20 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t>2020-10-23</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>135</v>
+        <v>14</v>
       </c>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>Ross-HR, Ross-Employees, Ross-Vendors</t>
+          <t>Ross-Finance, Ross-IT-Admins, Ross-HR</t>
         </is>
       </c>
       <c r="I28" s="17" t="inlineStr">
@@ -2428,20 +2409,20 @@
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2023-05-07</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G29" s="14" t="n">
-        <v>33</v>
+        <v>194</v>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Ross-Vendors</t>
+          <t>Ross-HR, Ross-Employees</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
@@ -2478,20 +2459,20 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G30" s="17" t="n">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>Ross-Employees, Ross-Contractors</t>
+          <t>Ross-Employees, Ross-HR</t>
         </is>
       </c>
       <c r="I30" s="17" t="inlineStr">
@@ -2528,20 +2509,20 @@
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>2022-02-14</t>
+          <t>2022-07-16</t>
         </is>
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G31" s="14" t="n">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>Ross-Contractors</t>
+          <t>Ross-Contractors, Ross-IT-Admins</t>
         </is>
       </c>
       <c r="I31" s="14" t="inlineStr">
@@ -2578,20 +2559,20 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2023-04-25</t>
         </is>
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G32" s="17" t="n">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>Ross-Contractors, Ross-Employees</t>
+          <t>Ross-Vendors, Ross-IT-Admins, Ross-Contractors</t>
         </is>
       </c>
       <c r="I32" s="17" t="inlineStr">
@@ -2704,17 +2685,17 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G3" s="14" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H3" s="14" t="inlineStr">
@@ -2746,17 +2727,17 @@
       </c>
       <c r="E4" s="17" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H4" s="17" t="inlineStr">
@@ -2788,12 +2769,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2830,12 +2811,12 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
@@ -2872,17 +2853,17 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
@@ -2914,17 +2895,17 @@
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
@@ -2956,17 +2937,17 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
@@ -2998,12 +2979,12 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
@@ -3040,17 +3021,17 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H11" s="14" t="inlineStr">
@@ -3082,17 +3063,17 @@
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
@@ -3124,17 +3105,17 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H13" s="14" t="inlineStr">
@@ -3166,17 +3147,17 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
@@ -3208,17 +3189,17 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H15" s="14" t="inlineStr">
@@ -3250,17 +3231,17 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
@@ -3292,17 +3273,17 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
@@ -3334,7 +3315,7 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="F18" s="17" t="inlineStr">
@@ -3344,7 +3325,7 @@
       </c>
       <c r="G18" s="17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H18" s="17" t="inlineStr">
@@ -3376,17 +3357,17 @@
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
@@ -3418,17 +3399,17 @@
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H20" s="17" t="inlineStr">
@@ -3460,17 +3441,17 @@
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
@@ -3502,17 +3483,17 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
@@ -3544,17 +3525,17 @@
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
@@ -3586,17 +3567,17 @@
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H24" s="17" t="inlineStr">
@@ -3628,17 +3609,17 @@
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
@@ -3670,17 +3651,17 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr">
@@ -3712,17 +3693,17 @@
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H27" s="14" t="inlineStr">
@@ -3754,17 +3735,17 @@
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H28" s="17" t="inlineStr">
@@ -3796,17 +3777,17 @@
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
@@ -3838,12 +3819,12 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr">
@@ -3880,17 +3861,17 @@
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
@@ -3922,12 +3903,12 @@
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="F32" s="17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr">
@@ -3964,17 +3945,17 @@
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
@@ -4006,17 +3987,17 @@
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F34" s="17" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G34" s="17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H34" s="17" t="inlineStr">
@@ -4048,17 +4029,17 @@
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
@@ -4090,17 +4071,17 @@
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="F36" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G36" s="17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H36" s="17" t="inlineStr">
@@ -4132,17 +4113,17 @@
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
@@ -4174,12 +4155,12 @@
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G38" s="17" t="inlineStr">
@@ -4216,17 +4197,17 @@
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
@@ -4258,17 +4239,17 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
@@ -4300,12 +4281,12 @@
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
@@ -4342,17 +4323,17 @@
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G42" s="17" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H42" s="17" t="inlineStr">
@@ -4384,17 +4365,17 @@
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
@@ -4426,17 +4407,17 @@
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="F44" s="17" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G44" s="17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H44" s="17" t="inlineStr">
@@ -4468,17 +4449,17 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
@@ -4515,12 +4496,12 @@
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
@@ -4552,17 +4533,17 @@
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
@@ -4594,17 +4575,17 @@
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G48" s="17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H48" s="17" t="inlineStr">
@@ -4636,17 +4617,17 @@
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
@@ -4678,17 +4659,17 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G50" s="17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H50" s="17" t="inlineStr">
@@ -4720,17 +4701,17 @@
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H51" s="14" t="inlineStr">
@@ -4762,17 +4743,17 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="F52" s="17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G52" s="17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H52" s="17" t="inlineStr">
@@ -4804,17 +4785,17 @@
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="F53" s="14" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H53" s="14" t="inlineStr">
@@ -4846,17 +4827,17 @@
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G54" s="17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H54" s="17" t="inlineStr">
@@ -4888,17 +4869,17 @@
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="F55" s="14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H55" s="14" t="inlineStr">
@@ -4930,17 +4911,17 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="F56" s="17" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G56" s="17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H56" s="17" t="inlineStr">
@@ -4972,17 +4953,17 @@
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="F57" s="14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H57" s="14" t="inlineStr">
@@ -5014,12 +4995,12 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G58" s="17" t="inlineStr">
@@ -5056,17 +5037,17 @@
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="F59" s="14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H59" s="14" t="inlineStr">
@@ -5098,17 +5079,17 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="F60" s="17" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
@@ -5145,12 +5126,12 @@
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H61" s="14" t="inlineStr">
@@ -5182,17 +5163,17 @@
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="F62" s="17" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
@@ -5229,7 +5210,7 @@
       </c>
       <c r="F63" s="14" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">
@@ -5266,17 +5247,17 @@
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="F64" s="17" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H64" s="17" t="inlineStr">
@@ -5308,17 +5289,17 @@
       </c>
       <c r="E65" s="14" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="F65" s="14" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G65" s="14" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H65" s="14" t="inlineStr">
@@ -5350,17 +5331,17 @@
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="F66" s="17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G66" s="17" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H66" s="17" t="inlineStr">
@@ -5392,17 +5373,17 @@
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H67" s="14" t="inlineStr">
@@ -5434,17 +5415,17 @@
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="F68" s="17" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H68" s="17" t="inlineStr">
@@ -5476,17 +5457,17 @@
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="F69" s="14" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H69" s="14" t="inlineStr">
@@ -5518,17 +5499,17 @@
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="F70" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G70" s="17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H70" s="17" t="inlineStr">
@@ -5560,17 +5541,17 @@
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="F71" s="14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H71" s="14" t="inlineStr">
@@ -5602,17 +5583,17 @@
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="F72" s="17" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G72" s="17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H72" s="17" t="inlineStr">
@@ -5644,17 +5625,17 @@
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="F73" s="14" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H73" s="14" t="inlineStr">
@@ -5686,17 +5667,17 @@
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F74" s="17" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G74" s="17" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H74" s="17" t="inlineStr">
@@ -5728,17 +5709,17 @@
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="F75" s="14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H75" s="14" t="inlineStr">
@@ -5770,17 +5751,17 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G76" s="17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H76" s="17" t="inlineStr">
@@ -5812,17 +5793,17 @@
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="F77" s="14" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G77" s="14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H77" s="14" t="inlineStr">
@@ -5854,17 +5835,17 @@
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G78" s="17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H78" s="17" t="inlineStr">
@@ -5896,17 +5877,17 @@
       </c>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H79" s="14" t="inlineStr">
@@ -5938,17 +5919,17 @@
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t>2020-11-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="F80" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G80" s="17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H80" s="17" t="inlineStr">
@@ -5980,17 +5961,17 @@
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="F81" s="14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G81" s="14" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H81" s="14" t="inlineStr">
@@ -6022,17 +6003,17 @@
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G82" s="17" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H82" s="17" t="inlineStr">
@@ -6064,17 +6045,17 @@
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F83" s="14" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G83" s="14" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H83" s="14" t="inlineStr">
@@ -6106,17 +6087,17 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G84" s="17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H84" s="17" t="inlineStr">
@@ -6148,17 +6129,17 @@
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="F85" s="14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G85" s="14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H85" s="14" t="inlineStr">
@@ -6190,17 +6171,17 @@
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>2023-07-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G86" s="17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H86" s="17" t="inlineStr">
@@ -6232,17 +6213,17 @@
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="F87" s="14" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G87" s="14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H87" s="14" t="inlineStr">
@@ -6274,17 +6255,17 @@
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="F88" s="17" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G88" s="17" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H88" s="17" t="inlineStr">
@@ -6316,17 +6297,17 @@
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="F89" s="14" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G89" s="14" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H89" s="14" t="inlineStr">
@@ -6358,17 +6339,17 @@
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="F90" s="17" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G90" s="17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H90" s="17" t="inlineStr">
@@ -6400,12 +6381,12 @@
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="F91" s="14" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G91" s="14" t="inlineStr">
@@ -6442,17 +6423,17 @@
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="F92" s="17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G92" s="17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H92" s="17" t="inlineStr">
@@ -6484,17 +6465,17 @@
       </c>
       <c r="E93" s="14" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="F93" s="14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G93" s="14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H93" s="14" t="inlineStr">
@@ -6526,17 +6507,17 @@
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="F94" s="17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G94" s="17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H94" s="17" t="inlineStr">
@@ -6568,17 +6549,17 @@
       </c>
       <c r="E95" s="14" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="F95" s="14" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G95" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H95" s="14" t="inlineStr">
@@ -6610,17 +6591,17 @@
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="F96" s="17" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G96" s="17" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H96" s="17" t="inlineStr">
@@ -6652,17 +6633,17 @@
       </c>
       <c r="E97" s="14" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="F97" s="14" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G97" s="14" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H97" s="14" t="inlineStr">
@@ -6694,12 +6675,12 @@
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t>2024-03-01</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="F98" s="17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G98" s="17" t="inlineStr">
@@ -6736,17 +6717,17 @@
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="F99" s="14" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G99" s="14" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H99" s="14" t="inlineStr">
@@ -6778,17 +6759,17 @@
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="F100" s="17" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G100" s="17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H100" s="17" t="inlineStr">
@@ -6820,17 +6801,17 @@
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="F101" s="14" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G101" s="14" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H101" s="14" t="inlineStr">
@@ -6862,17 +6843,17 @@
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="F102" s="17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G102" s="17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H102" s="17" t="inlineStr">
@@ -6904,17 +6885,17 @@
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="F103" s="14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G103" s="14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H103" s="14" t="inlineStr">
@@ -6946,17 +6927,17 @@
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="F104" s="17" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G104" s="17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H104" s="17" t="inlineStr">
@@ -6988,17 +6969,17 @@
       </c>
       <c r="E105" s="14" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="F105" s="14" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G105" s="14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H105" s="14" t="inlineStr">
@@ -7030,17 +7011,17 @@
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="F106" s="17" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="G106" s="17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H106" s="17" t="inlineStr">
@@ -7072,12 +7053,12 @@
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="F107" s="14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="G107" s="14" t="inlineStr">
@@ -7114,17 +7095,17 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="F108" s="17" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G108" s="17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H108" s="17" t="inlineStr">
@@ -7156,17 +7137,17 @@
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="F109" s="14" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G109" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H109" s="14" t="inlineStr">
@@ -7198,12 +7179,12 @@
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="F110" s="17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G110" s="17" t="inlineStr">
@@ -7240,17 +7221,17 @@
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="F111" s="14" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G111" s="14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H111" s="14" t="inlineStr">
@@ -7282,17 +7263,17 @@
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="F112" s="17" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G112" s="17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H112" s="17" t="inlineStr">
@@ -7324,17 +7305,17 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="F113" s="14" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G113" s="14" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H113" s="14" t="inlineStr">
@@ -7366,17 +7347,17 @@
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t>2020-05-01</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="F114" s="17" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G114" s="17" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H114" s="17" t="inlineStr">
@@ -7408,12 +7389,12 @@
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="F115" s="14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G115" s="14" t="inlineStr">
@@ -7450,17 +7431,17 @@
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="F116" s="17" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G116" s="17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H116" s="17" t="inlineStr">
@@ -7492,17 +7473,17 @@
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="F117" s="14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G117" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H117" s="14" t="inlineStr">
@@ -7534,17 +7515,17 @@
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="F118" s="17" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G118" s="17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H118" s="17" t="inlineStr">
@@ -7576,17 +7557,17 @@
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="F119" s="14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G119" s="14" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H119" s="14" t="inlineStr">
@@ -7618,17 +7599,17 @@
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t>2020-08-01</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="F120" s="17" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G120" s="17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H120" s="17" t="inlineStr">
@@ -7660,17 +7641,17 @@
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="F121" s="14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G121" s="14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H121" s="14" t="inlineStr">
@@ -7702,17 +7683,17 @@
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F122" s="17" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G122" s="17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H122" s="17" t="inlineStr">
@@ -7744,17 +7725,17 @@
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="F123" s="14" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G123" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H123" s="14" t="inlineStr">
@@ -7786,17 +7767,17 @@
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="F124" s="17" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G124" s="17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H124" s="17" t="inlineStr">
@@ -7828,17 +7809,17 @@
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="F125" s="14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G125" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H125" s="14" t="inlineStr">
@@ -7870,17 +7851,17 @@
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="F126" s="17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G126" s="17" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H126" s="17" t="inlineStr">
@@ -7912,17 +7893,17 @@
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="F127" s="14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G127" s="14" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H127" s="14" t="inlineStr">
@@ -7954,17 +7935,17 @@
       </c>
       <c r="E128" s="17" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="F128" s="17" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G128" s="17" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H128" s="17" t="inlineStr">
@@ -7996,17 +7977,17 @@
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="F129" s="14" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G129" s="14" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H129" s="14" t="inlineStr">
@@ -8038,17 +8019,17 @@
       </c>
       <c r="E130" s="17" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="F130" s="17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G130" s="17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H130" s="17" t="inlineStr">
@@ -8080,17 +8061,17 @@
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>2020-09-01</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="F131" s="14" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G131" s="14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H131" s="14" t="inlineStr">
@@ -8122,17 +8103,17 @@
       </c>
       <c r="E132" s="17" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="F132" s="17" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G132" s="17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H132" s="17" t="inlineStr">
@@ -8164,12 +8145,12 @@
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="F133" s="14" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G133" s="14" t="inlineStr">
@@ -8206,17 +8187,17 @@
       </c>
       <c r="E134" s="17" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="F134" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G134" s="17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H134" s="17" t="inlineStr">
@@ -8253,12 +8234,12 @@
       </c>
       <c r="F135" s="14" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G135" s="14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H135" s="14" t="inlineStr">
@@ -8290,17 +8271,17 @@
       </c>
       <c r="E136" s="17" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="F136" s="17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G136" s="17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H136" s="17" t="inlineStr">
@@ -8332,17 +8313,17 @@
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="F137" s="14" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G137" s="14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H137" s="14" t="inlineStr">
@@ -8374,17 +8355,17 @@
       </c>
       <c r="E138" s="17" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="F138" s="17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G138" s="17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H138" s="17" t="inlineStr">
@@ -8416,17 +8397,17 @@
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>2020-02-01</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="F139" s="14" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G139" s="14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H139" s="14" t="inlineStr">
@@ -8458,17 +8439,17 @@
       </c>
       <c r="E140" s="17" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="F140" s="17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G140" s="17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H140" s="17" t="inlineStr">
@@ -8500,17 +8481,17 @@
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="F141" s="14" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G141" s="14" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H141" s="14" t="inlineStr">
@@ -8542,17 +8523,17 @@
       </c>
       <c r="E142" s="17" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="F142" s="17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G142" s="17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H142" s="17" t="inlineStr">
@@ -8584,17 +8565,17 @@
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="F143" s="14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G143" s="14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H143" s="14" t="inlineStr">
@@ -8626,17 +8607,17 @@
       </c>
       <c r="E144" s="17" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="F144" s="17" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G144" s="17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H144" s="17" t="inlineStr">
@@ -8668,17 +8649,17 @@
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="F145" s="14" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G145" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H145" s="14" t="inlineStr">
@@ -8710,17 +8691,17 @@
       </c>
       <c r="E146" s="17" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="F146" s="17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G146" s="17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H146" s="17" t="inlineStr">
@@ -8752,17 +8733,17 @@
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="F147" s="14" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G147" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="H147" s="14" t="inlineStr">
@@ -8794,17 +8775,17 @@
       </c>
       <c r="E148" s="17" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="F148" s="17" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G148" s="17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H148" s="17" t="inlineStr">
@@ -8836,17 +8817,17 @@
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>2023-04-01</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="F149" s="14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G149" s="14" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H149" s="14" t="inlineStr">
@@ -8878,17 +8859,17 @@
       </c>
       <c r="E150" s="17" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="F150" s="17" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G150" s="17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H150" s="17" t="inlineStr">
@@ -8920,17 +8901,17 @@
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="F151" s="14" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G151" s="14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H151" s="14" t="inlineStr">
@@ -8962,17 +8943,17 @@
       </c>
       <c r="E152" s="17" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="F152" s="17" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G152" s="17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H152" s="17" t="inlineStr">
@@ -9004,17 +8985,17 @@
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="F153" s="14" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G153" s="14" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G153" s="14" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H153" s="14" t="inlineStr">
@@ -9046,17 +9027,17 @@
       </c>
       <c r="E154" s="17" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="F154" s="17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G154" s="17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H154" s="17" t="inlineStr">
@@ -9088,12 +9069,12 @@
       </c>
       <c r="E155" s="14" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="F155" s="14" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G155" s="14" t="inlineStr">
@@ -9130,12 +9111,12 @@
       </c>
       <c r="E156" s="17" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="F156" s="17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G156" s="17" t="inlineStr">
@@ -9172,17 +9153,17 @@
       </c>
       <c r="E157" s="14" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="F157" s="14" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G157" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H157" s="14" t="inlineStr">
@@ -9214,17 +9195,17 @@
       </c>
       <c r="E158" s="17" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="F158" s="17" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G158" s="17" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G158" s="17" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H158" s="17" t="inlineStr">
@@ -9256,17 +9237,17 @@
       </c>
       <c r="E159" s="14" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="F159" s="14" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G159" s="14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H159" s="14" t="inlineStr">
@@ -9298,12 +9279,12 @@
       </c>
       <c r="E160" s="17" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="F160" s="17" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G160" s="17" t="inlineStr">
@@ -9340,17 +9321,17 @@
       </c>
       <c r="E161" s="14" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="F161" s="14" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G161" s="14" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G161" s="14" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H161" s="14" t="inlineStr">
@@ -9382,17 +9363,17 @@
       </c>
       <c r="E162" s="17" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="F162" s="17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G162" s="17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H162" s="17" t="inlineStr">
@@ -9424,17 +9405,17 @@
       </c>
       <c r="E163" s="14" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="F163" s="14" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G163" s="14" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G163" s="14" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H163" s="14" t="inlineStr">
@@ -9466,17 +9447,17 @@
       </c>
       <c r="E164" s="17" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="F164" s="17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G164" s="17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H164" s="17" t="inlineStr">
@@ -9508,12 +9489,12 @@
       </c>
       <c r="E165" s="14" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="F165" s="14" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G165" s="14" t="inlineStr">
@@ -9550,12 +9531,12 @@
       </c>
       <c r="E166" s="17" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="F166" s="17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G166" s="17" t="inlineStr">
@@ -9592,17 +9573,17 @@
       </c>
       <c r="E167" s="14" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="F167" s="14" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G167" s="14" t="inlineStr">
+        <is>
           <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G167" s="14" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H167" s="14" t="inlineStr">
@@ -9634,17 +9615,17 @@
       </c>
       <c r="E168" s="17" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="F168" s="17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G168" s="17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H168" s="17" t="inlineStr">
@@ -9676,12 +9657,12 @@
       </c>
       <c r="E169" s="14" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="F169" s="14" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G169" s="14" t="inlineStr">
@@ -9718,12 +9699,12 @@
       </c>
       <c r="E170" s="17" t="inlineStr">
         <is>
-          <t>2021-07-01</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="F170" s="17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G170" s="17" t="inlineStr">
@@ -9760,17 +9741,17 @@
       </c>
       <c r="E171" s="14" t="inlineStr">
         <is>
-          <t>2021-10-01</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="F171" s="14" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G171" s="14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H171" s="14" t="inlineStr">
@@ -9802,17 +9783,17 @@
       </c>
       <c r="E172" s="17" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="F172" s="17" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G172" s="17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H172" s="17" t="inlineStr">
@@ -9844,17 +9825,17 @@
       </c>
       <c r="E173" s="14" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="F173" s="14" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G173" s="14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H173" s="14" t="inlineStr">
@@ -9886,12 +9867,12 @@
       </c>
       <c r="E174" s="17" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="F174" s="17" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="G174" s="17" t="inlineStr">
@@ -10694,44 +10675,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>POLICIES (12 total)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="31" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>Policy Name</t>
         </is>
       </c>
-      <c r="B2" s="31" t="inlineStr">
+      <c r="B2" s="25" t="inlineStr">
         <is>
           <t>Policy Type</t>
         </is>
       </c>
-      <c r="C2" s="31" t="inlineStr">
+      <c r="C2" s="25" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D2" s="31" t="inlineStr">
+      <c r="D2" s="25" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="E2" s="31" t="inlineStr">
+      <c r="E2" s="25" t="inlineStr">
         <is>
           <t>Created</t>
         </is>
       </c>
-      <c r="F2" s="31" t="inlineStr">
+      <c r="F2" s="25" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
       </c>
-      <c r="G2" s="31" t="inlineStr">
+      <c r="G2" s="25" t="inlineStr">
         <is>
           <t>Policy ID</t>
         </is>
@@ -10813,7 +10794,7 @@
           <t>High Security Apps</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>Password</t>
         </is>
@@ -11058,7 +11039,7 @@
           <t>High Security Apps</t>
         </is>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Password</t>
         </is>
@@ -11185,56 +11166,56 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="33" t="inlineStr">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>OKTA ACCESS GATEWAY (OAG) APPLICATIONS (1 identified)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="34" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>ℹ️  OAG apps are identified by label keywords. Please review and update manually if needed.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>App Name</t>
         </is>
       </c>
-      <c r="B3" s="35" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C3" s="35" t="inlineStr">
+      <c r="C3" s="33" t="inlineStr">
         <is>
           <t>Sign-On Mode</t>
         </is>
       </c>
-      <c r="D3" s="35" t="inlineStr">
+      <c r="D3" s="33" t="inlineStr">
         <is>
           <t>Created</t>
         </is>
       </c>
-      <c r="E3" s="35" t="inlineStr">
+      <c r="E3" s="33" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
       </c>
-      <c r="F3" s="35" t="inlineStr">
+      <c r="F3" s="33" t="inlineStr">
         <is>
           <t>App ID</t>
         </is>
       </c>
-      <c r="G3" s="35" t="inlineStr">
+      <c r="G3" s="33" t="inlineStr">
         <is>
           <t>Backend URL</t>
         </is>
       </c>
-      <c r="H3" s="35" t="inlineStr">
+      <c r="H3" s="33" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -11258,12 +11239,12 @@
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>2023-03-18</t>
+          <t>2021-04-03</t>
         </is>
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="F4" s="14" t="inlineStr">
@@ -11299,14 +11280,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="36" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>MANUAL INVENTORY — Items to Fill In</t>
         </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>OAG CONFIGURATION</t>
         </is>
@@ -11318,8 +11299,8 @@
           <t>OAG Version</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr"/>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr"/>
+      <c r="C4" s="36" t="inlineStr">
         <is>
           <t>e.g. 2024.09.0</t>
         </is>
@@ -11331,8 +11312,8 @@
           <t>Number of OAG Instances</t>
         </is>
       </c>
-      <c r="B5" s="38" t="inlineStr"/>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr"/>
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>e.g. 2</t>
         </is>
@@ -11344,8 +11325,8 @@
           <t>OAG Server IPs/Hostnames</t>
         </is>
       </c>
-      <c r="B6" s="38" t="inlineStr"/>
-      <c r="C6" s="39" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr"/>
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>e.g. cooaggtwprd01, cooaggtwprd02</t>
         </is>
@@ -11357,8 +11338,8 @@
           <t>OAG High Availability</t>
         </is>
       </c>
-      <c r="B7" s="38" t="inlineStr"/>
-      <c r="C7" s="39" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr"/>
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
@@ -11370,15 +11351,15 @@
           <t>OAG Protected Apps Count</t>
         </is>
       </c>
-      <c r="B8" s="38" t="inlineStr"/>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr"/>
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>Total apps behind OAG</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>LIFECYCLE MANAGEMENT</t>
         </is>
@@ -11390,8 +11371,8 @@
           <t>Provisioning Connectors Active</t>
         </is>
       </c>
-      <c r="B11" s="38" t="inlineStr"/>
-      <c r="C11" s="39" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr"/>
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>e.g. Active Directory, Workday</t>
         </is>
@@ -11403,8 +11384,8 @@
           <t>Deprovisioning Automated</t>
         </is>
       </c>
-      <c r="B12" s="38" t="inlineStr"/>
-      <c r="C12" s="39" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr"/>
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>Yes / No / Partial</t>
         </is>
@@ -11416,8 +11397,8 @@
           <t>Joiner-Mover-Leaver Workflow</t>
         </is>
       </c>
-      <c r="B13" s="38" t="inlineStr"/>
-      <c r="C13" s="39" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr"/>
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>Configured / Not Configured</t>
         </is>
@@ -11429,8 +11410,8 @@
           <t>HR System Integration</t>
         </is>
       </c>
-      <c r="B14" s="38" t="inlineStr"/>
-      <c r="C14" s="39" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr"/>
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>e.g. Workday, SAP</t>
         </is>
@@ -11442,15 +11423,15 @@
           <t>Okta Workflows Used</t>
         </is>
       </c>
-      <c r="B15" s="38" t="inlineStr"/>
-      <c r="C15" s="39" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr"/>
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>Yes / No — list flows if yes</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>MFA &amp; AUTHENTICATION</t>
         </is>
@@ -11462,8 +11443,8 @@
           <t>MFA Methods Enabled</t>
         </is>
       </c>
-      <c r="B18" s="38" t="inlineStr"/>
-      <c r="C18" s="39" t="inlineStr">
+      <c r="B18" s="35" t="inlineStr"/>
+      <c r="C18" s="36" t="inlineStr">
         <is>
           <t>e.g. Okta Verify, SMS, TOTP</t>
         </is>
@@ -11475,8 +11456,8 @@
           <t>Passwordless Enabled</t>
         </is>
       </c>
-      <c r="B19" s="38" t="inlineStr"/>
-      <c r="C19" s="39" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr"/>
+      <c r="C19" s="36" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
@@ -11488,8 +11469,8 @@
           <t>Okta FastPass Used</t>
         </is>
       </c>
-      <c r="B20" s="38" t="inlineStr"/>
-      <c r="C20" s="39" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr"/>
+      <c r="C20" s="36" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
@@ -11501,8 +11482,8 @@
           <t>Device Trust Configured</t>
         </is>
       </c>
-      <c r="B21" s="38" t="inlineStr"/>
-      <c r="C21" s="39" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr"/>
+      <c r="C21" s="36" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
@@ -11514,15 +11495,15 @@
           <t>Risk-Based Authentication</t>
         </is>
       </c>
-      <c r="B22" s="38" t="inlineStr"/>
-      <c r="C22" s="39" t="inlineStr">
+      <c r="B22" s="35" t="inlineStr"/>
+      <c r="C22" s="36" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="37" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>DIRECTORIES</t>
         </is>
@@ -11534,8 +11515,8 @@
           <t>Active Directory Domains</t>
         </is>
       </c>
-      <c r="B25" s="38" t="inlineStr"/>
-      <c r="C25" s="39" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr"/>
+      <c r="C25" s="36" t="inlineStr">
         <is>
           <t>List all connected AD domains</t>
         </is>
@@ -11547,8 +11528,8 @@
           <t>AD Agent Version</t>
         </is>
       </c>
-      <c r="B26" s="38" t="inlineStr"/>
-      <c r="C26" s="39" t="inlineStr">
+      <c r="B26" s="35" t="inlineStr"/>
+      <c r="C26" s="36" t="inlineStr">
         <is>
           <t>e.g. 3.17.0</t>
         </is>
@@ -11560,8 +11541,8 @@
           <t>LDAP Directories</t>
         </is>
       </c>
-      <c r="B27" s="38" t="inlineStr"/>
-      <c r="C27" s="39" t="inlineStr">
+      <c r="B27" s="35" t="inlineStr"/>
+      <c r="C27" s="36" t="inlineStr">
         <is>
           <t>List if any</t>
         </is>
@@ -11573,8 +11554,8 @@
           <t>HR-Mastered Attributes</t>
         </is>
       </c>
-      <c r="B28" s="38" t="inlineStr"/>
-      <c r="C28" s="39" t="inlineStr">
+      <c r="B28" s="35" t="inlineStr"/>
+      <c r="C28" s="36" t="inlineStr">
         <is>
           <t>List attributes mastered from HR</t>
         </is>
@@ -11586,15 +11567,15 @@
           <t>Profile Master Source</t>
         </is>
       </c>
-      <c r="B29" s="38" t="inlineStr"/>
-      <c r="C29" s="39" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr"/>
+      <c r="C29" s="36" t="inlineStr">
         <is>
           <t>e.g. Active Directory / Okta</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="37" t="inlineStr">
+      <c r="A31" s="34" t="inlineStr">
         <is>
           <t>GOVERNANCE &amp; COMPLIANCE</t>
         </is>
@@ -11606,8 +11587,8 @@
           <t>Okta System Log Retention</t>
         </is>
       </c>
-      <c r="B32" s="38" t="inlineStr"/>
-      <c r="C32" s="39" t="inlineStr">
+      <c r="B32" s="35" t="inlineStr"/>
+      <c r="C32" s="36" t="inlineStr">
         <is>
           <t>Days retained</t>
         </is>
@@ -11619,8 +11600,8 @@
           <t>SIEM Integration</t>
         </is>
       </c>
-      <c r="B33" s="38" t="inlineStr"/>
-      <c r="C33" s="39" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr"/>
+      <c r="C33" s="36" t="inlineStr">
         <is>
           <t>e.g. Splunk, Sentinel</t>
         </is>
@@ -11632,8 +11613,8 @@
           <t>Admin Roles in Use</t>
         </is>
       </c>
-      <c r="B34" s="38" t="inlineStr"/>
-      <c r="C34" s="39" t="inlineStr">
+      <c r="B34" s="35" t="inlineStr"/>
+      <c r="C34" s="36" t="inlineStr">
         <is>
           <t>List super admin count</t>
         </is>
@@ -11645,8 +11626,8 @@
           <t>Break-Glass Accounts</t>
         </is>
       </c>
-      <c r="B35" s="38" t="inlineStr"/>
-      <c r="C35" s="39" t="inlineStr">
+      <c r="B35" s="35" t="inlineStr"/>
+      <c r="C35" s="36" t="inlineStr">
         <is>
           <t>Count and location</t>
         </is>
@@ -11658,15 +11639,15 @@
           <t>Last Security Review Date</t>
         </is>
       </c>
-      <c r="B36" s="38" t="inlineStr"/>
-      <c r="C36" s="39" t="inlineStr">
+      <c r="B36" s="35" t="inlineStr"/>
+      <c r="C36" s="36" t="inlineStr">
         <is>
           <t>MM/YYYY</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="40" t="inlineStr">
+      <c r="A39" s="37" t="inlineStr">
         <is>
           <t>🟡 Yellow cells = Fill in manually     🔵 Blue cells = Labels     ℹ️ Grey cells = Hints</t>
         </is>
